--- a/reports/pdf_weekly_20260911.xlsx
+++ b/reports/pdf_weekly_20260911.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-09-07 ~ 2026-09-11  (5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>주간 변화  ·  2026-09-07 ~ 2026-09-11  (5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,595억   ·   현금 31억(0.7%)      주말 2026-09-11  vs  주초 2026-09-07      매수 10종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,659억   ·   현금 15억(0.3%)      주말 2026-09-11  vs  주초 2026-09-07      매수 10종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>935</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>6727624200</v>
+        <v>6681089250</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1540770000</v>
+        <v>-1530112500</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3588248400</v>
+        <v>3563428500</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-43</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-308528440</v>
+        <v>-306394350</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1968947200</v>
+        <v>1955328000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-39</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-10932636000</v>
+        <v>-10857015000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1374700800</v>
+        <v>1365192000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1176753600</v>
+        <v>-1168614000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>918086400</v>
+        <v>911736000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-26</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1294550400</v>
+        <v>-1285596000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>970912800</v>
+        <v>964197000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-24</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-7857168000</v>
+        <v>-7802820000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>10590580000</v>
+        <v>10517325000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-23</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1834148800</v>
+        <v>-1821462000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1415383200</v>
+        <v>1405593000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-21</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-936150600</v>
+        <v>-929675250</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1411740000</v>
+        <v>1401975000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-766286400</v>
+        <v>-817668000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.09%→0.81%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>824274000</v>
+        <v>818572500</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-823363200</v>
+        <v>-760986000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.81%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
         <v>-9</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-797860800</v>
+        <v>-792342000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,531억   ·   현금 87억(2.5%)      주말 2026-09-11  vs  주초 2026-09-07      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,489억   ·   현금 43억(1.2%)      주말 2026-09-11  vs  주초 2026-09-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1155,7 +1155,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,613억   ·   현금 84억(3.1%)      주말 2026-09-11  vs  주초 2026-09-07      매수 9종목  /  매도 9종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,638억   ·   현금 42억(1.6%)      주말 2026-09-11  vs  주초 2026-09-07      매수 9종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1251,7 +1251,7 @@
         <v>97</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>521297400</v>
+        <v>519784200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>-224</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1552620160</v>
+        <v>-1548113280</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>77</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>2594291700</v>
+        <v>2586761100</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>-150</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-2113507500</v>
+        <v>-2107372500</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>60</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>4026516000</v>
+        <v>4014828000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>-105</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1559034750</v>
+        <v>-1554509250</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>5572287500</v>
+        <v>5556112500</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>-99</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1320564960</v>
+        <v>-1316731680</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>2454700300</v>
+        <v>2447574900</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>-96</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-8856681600</v>
+        <v>-8830972800</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>18</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>623820600</v>
+        <v>622009800</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>-65</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2008607250</v>
+        <v>-2002776750</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>3167677500</v>
+        <v>3158482500</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>-63</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-2135624400</v>
+        <v>-2129425200</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>516887800</v>
+        <v>515387400</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>-50</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1663935000</v>
+        <v>-1659105000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1567475000</v>
+        <v>1562925000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>-30</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-695545500</v>
+        <v>-693526500</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,000억   ·   현금 9억(0.5%)      주말 2026-09-11  vs  주초 2026-09-07      매수 7종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,974억   ·   현금 5억(0.2%)      주말 2026-09-11  vs  주초 2026-09-07      매수 7종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -2019,432 +2019,82 @@
       <c r="K43" s="17" t="n"/>
     </row>
     <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 2억(0.6%)      주말 2026-09-11  vs  주초 2026-09-07      매수 5종목  /  매도 7종목</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="20" t="n"/>
+      <c r="G45" s="20" t="n"/>
+      <c r="H45" s="20" t="n"/>
+      <c r="I45" s="20" t="n"/>
+      <c r="J45" s="20" t="n"/>
+      <c r="K45" s="20" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 493억   ·   현금 4억(0.8%)      주말 2026-09-11  vs  주초 2026-09-07      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>274</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>192567200</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>6.84%→7.51%</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>2,706→2,980</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>-64960000</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>5.31%→5.06%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>909→869</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>선익시스템</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>185913000</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>0.33%→0.99%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>19→58</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-37</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-116420500</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>4.05%→3.62%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>358→321</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>84294000</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>1.12%→1.42%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>100→127</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>원익머트리얼즈</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-29393000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>2.13%→2.02%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>262→249</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>40131000</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>1.63%→1.77%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>293→319</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-22396500</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>0.99%→0.91%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>111→102</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>대주전자재료</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>24472000</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>1.74%→1.82%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>79→83</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-85344000</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>3.72%→3.41%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>97→89</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-58849000</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>2.57%→2.35%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>85→78</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="17" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>-66710000</v>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>1.82%→1.58%</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>38→33</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 500억   ·   현금 8억(1.7%)      주말 2026-09-11  vs  주초 2026-09-07      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="19" t="inlineStr">
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n"/>
-      <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="20" t="n"/>
-      <c r="G59" s="20" t="n"/>
-      <c r="H59" s="20" t="n"/>
-      <c r="I59" s="20" t="n"/>
-      <c r="J59" s="20" t="n"/>
-      <c r="K59" s="20" t="n"/>
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="20" t="n"/>
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="20" t="n"/>
+      <c r="F50" s="20" t="n"/>
+      <c r="G50" s="20" t="n"/>
+      <c r="H50" s="20" t="n"/>
+      <c r="I50" s="20" t="n"/>
+      <c r="J50" s="20" t="n"/>
+      <c r="K50" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="17">
     <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="A50:K50"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="G22:K22"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="G46:K46"/>
-    <mergeCell ref="G22:K22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_weekly_20260911.xlsx
+++ b/reports/pdf_weekly_20260911.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주간 변화  ·  2026-09-07 ~ 2026-09-11  (5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>주간 변화  ·  2026-09-07 ~ 2026-09-11  (5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -2019,82 +2019,432 @@
       <c r="K43" s="17" t="n"/>
     </row>
     <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="20" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="20" t="n"/>
-      <c r="H45" s="20" t="n"/>
-      <c r="I45" s="20" t="n"/>
-      <c r="J45" s="20" t="n"/>
-      <c r="K45" s="20" t="n"/>
-    </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억   ·   현금 1억(0.3%)      주말 2026-09-11  vs  주초 2026-09-07      매수 5종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>274</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>189882000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>6.69%→7.34%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>2,706→2,980</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-65240000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>5.29%→5.04%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>909→869</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>186186000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>0.32%→0.98%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>19→58</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-37</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-126651000</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>4.37%→3.91%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>358→321</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>82309500</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>1.09%→1.38%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>100→127</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-29484000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>2.12%→2.01%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>262→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>38675000</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>1.55%→1.69%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>293→319</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-22270500</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.98%→0.90%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>111→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>24360000</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>1.72%→1.80%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>79→83</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-86800000</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>3.75%→3.43%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>97→89</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="n"/>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-58212000</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>2.52%→2.31%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>85→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="n"/>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-66710000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>1.81%→1.57%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>38→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 493억   ·   현금 4억(0.8%)      주말 2026-09-11  vs  주초 2026-09-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="19" t="inlineStr">
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n"/>
-      <c r="C50" s="20" t="n"/>
-      <c r="D50" s="20" t="n"/>
-      <c r="E50" s="20" t="n"/>
-      <c r="F50" s="20" t="n"/>
-      <c r="G50" s="20" t="n"/>
-      <c r="H50" s="20" t="n"/>
-      <c r="I50" s="20" t="n"/>
-      <c r="J50" s="20" t="n"/>
-      <c r="K50" s="20" t="n"/>
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="20" t="n"/>
+      <c r="E59" s="20" t="n"/>
+      <c r="F59" s="20" t="n"/>
+      <c r="G59" s="20" t="n"/>
+      <c r="H59" s="20" t="n"/>
+      <c r="I59" s="20" t="n"/>
+      <c r="J59" s="20" t="n"/>
+      <c r="K59" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A56:K56"/>
     <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="G46:K46"/>
     <mergeCell ref="G22:K22"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_weekly_20260911.xlsx
+++ b/reports/pdf_weekly_20260911.xlsx
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-817668000</v>
+        <v>-760986000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.09%→0.81%</t>
+          <t>0.17%→0.00%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>67→55</t>
+          <t>12→0</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크  (편출)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-760986000</v>
+        <v>-817668000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.17%→0.00%</t>
+          <t>1.09%→0.81%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>67→55</t>
         </is>
       </c>
     </row>
